--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251206_201123.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251206_201123.xlsx
@@ -5384,7 +5384,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251206_201123.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251206_201123.xlsx
@@ -5384,7 +5384,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
